--- a/Imamiah Monney.xlsx
+++ b/Imamiah Monney.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Desktop\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF90C6A7-7EB8-4555-8DCC-BDB73179F422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40113B0-D551-4270-BCDB-6DC8647FFA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{596DA2EB-D571-4A09-BDC5-6CE0D1E545D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{596DA2EB-D571-4A09-BDC5-6CE0D1E545D6}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTNERSHIPS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>abandonné</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>digitale</t>
+  </si>
+  <si>
+    <t>En negociation</t>
   </si>
 </sst>
 </file>
@@ -204,12 +207,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -546,132 +547,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97281CE3-D9DA-44A8-BEE0-93A5672C9B5C}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>5000000</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="G3" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H3" s="2">
+        <v>500000</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="2">
+        <v>80000000</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8000000</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -700,405 +695,405 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="3">
         <v>46036</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="3">
         <v>46086</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>5000000</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>520</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>50000</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>1000</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>50</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>500</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>46037</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>46087</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>5000000</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>520</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>50000</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>1000</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>50</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>500</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>46038</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>46088</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>5000000</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>520</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>50000</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>1000</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>50</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>500</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>46039</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>46089</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>5000000</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>520</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>50000</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>1000</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>50</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>500</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>46040</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>46090</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>5000000</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>520</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>50000</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>1000</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>50</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>500</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="5">
+      <c r="D7" s="1"/>
+      <c r="E7" s="3">
         <v>46041</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>46091</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>5000000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>520</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>50000</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>1000</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>50</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>500</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Imamiah Monney.xlsx
+++ b/Imamiah Monney.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Desktop\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40113B0-D551-4270-BCDB-6DC8647FFA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE2B83F-9338-42DE-8543-C10AFA341DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{596DA2EB-D571-4A09-BDC5-6CE0D1E545D6}"/>
   </bookViews>
@@ -37,34 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
-  <si>
-    <t>abandonné</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        </t>
-  </si>
-  <si>
-    <t>Imamiah Monney</t>
-  </si>
-  <si>
-    <t>Entreprise</t>
-  </si>
-  <si>
-    <t>Banque</t>
-  </si>
-  <si>
-    <t>autre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signé </t>
-  </si>
-  <si>
-    <t>Referral</t>
-  </si>
-  <si>
-    <t>Prospection</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>nom_partenaire</t>
   </si>
@@ -81,9 +54,6 @@
     <t>statut</t>
   </si>
   <si>
-    <t xml:space="preserve"> origine_contact</t>
-  </si>
-  <si>
     <t>objectif_volume</t>
   </si>
   <si>
@@ -147,7 +117,13 @@
     <t>digitale</t>
   </si>
   <si>
-    <t>En negociation</t>
+    <t>origine_contact</t>
+  </si>
+  <si>
+    <t>Mail</t>
+  </si>
+  <si>
+    <t>Contact</t>
   </si>
 </sst>
 </file>
@@ -157,7 +133,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -170,6 +146,11 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +160,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -202,16 +183,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers [0]" xfId="1" builtinId="6"/>
@@ -547,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97281CE3-D9DA-44A8-BEE0-93A5672C9B5C}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -560,108 +559,72 @@
     <col min="8" max="8" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="H2" s="2">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>500000</v>
-      </c>
-      <c r="H3" s="2">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>80000000</v>
-      </c>
-      <c r="H4" s="2">
-        <v>8000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -696,53 +659,53 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3">
         <v>46036</v>
@@ -776,10 +739,10 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3">
         <v>46037</v>
@@ -811,10 +774,10 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3">
         <v>46038</v>
@@ -846,10 +809,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>46039</v>
@@ -881,10 +844,10 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3">
         <v>46040</v>
@@ -916,7 +879,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="3">
